--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3014,6 +3014,28 @@
       <c r="D54" s="26" t="inlineStr">
         <is>
           <t>축정의 9~10행 · 설정값 · 설정파라미터 · 안내 시트 표</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>식후 행동 판정 기준 추가 (10-14)</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>식후에 걸었는지 판정 기준이 없었음</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 CFG-086~088(5분 초과 이어 걷기 · 300보 · 운동 기록) 추가. 데이터계약 R-12와 같은 값</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 · 설정파라미터</t>
         </is>
       </c>
     </row>
@@ -55302,7 +55324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57457,6 +57479,114 @@
       <c r="H59" s="18" t="inlineStr">
         <is>
           <t>12:00~12:30 답 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_STREAK_MINUTES</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>MINUTE</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>5분을 넘어야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_STREAK_STEPS_PER_MINUTE</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>분당 걸음</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>CFG-087</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_TOTAL_STEPS</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>관찰 시간 합계</t>
         </is>
       </c>
     </row>
@@ -57475,7 +57605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60089,6 +60219,102 @@
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>식후 이어 걷기 기준</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>5분 초과 · 분당 20보 이상</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>식후 관찰 시간 안에 분당 20보 이상이 5분 넘게 이어지면 「걸었음」. 임시값</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>CFG-087</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>식후 합계 걸음 기준</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>300보</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>식후 관찰 시간 안 합계 300보 이상이면 「걸었음」. 임시값</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>CFG-088</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>식후 운동 기록 인정</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>관찰 시간 안에 운동 기록이 시작되면 「걸었음」</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -57391,7 +57391,7 @@
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="18" t="inlineStr">
@@ -57406,7 +57406,7 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>전체. 보통 5, 많으면 6</t>
         </is>
       </c>
     </row>
@@ -60146,7 +60146,7 @@
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>최대 1 · 식이 최대 3 · 전체 최대 5</t>
+          <t>최대 1 · 식이 최대 3 · 전체 최대 5~6</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 멈춤 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
+          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 선택지 상한 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
@@ -55277,7 +55277,7 @@
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>버튼은 7시 · 8시 정각 고정(아침 질문은 멈춤 시각 9시를 늘 지난 뒤). 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>버튼은 7시 · 8시 정각 고정(아침 질문은 선택지 상한 시각 9시를 늘 지난 뒤). 점수 · 등급 없음. 회전 후보 아님</t>
         </is>
       </c>
       <c r="K11" s="27" t="inlineStr">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 아침</t>
+          <t>선택지 상한 시각 · 아침</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 점심</t>
+          <t>선택지 상한 시각 · 점심</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -59917,7 +59917,7 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 저녁</t>
+          <t>선택지 상한 시각 · 저녁</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3036,6 +3036,28 @@
       <c r="D55" s="26" t="inlineStr">
         <is>
           <t>설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>시각 단계 선택지 글자 · 어제 저녁 질문 (10-14)</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>선택지 큰 글자가 시각이라 길고, 어제 저녁은 묻지 않았음</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
         </is>
       </c>
     </row>
@@ -54377,7 +54399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -55174,22 +55196,22 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>{t0} 이후 (1시간 이내)</t>
+          <t>1시간 이내 (작은 글씨 {t0} 이후)</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>{t1}~{t0} (1~2시간 전)</t>
+          <t>1~2시간 전 (작은 글씨 {t1}~{t0})</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>{t1} 이전 (그보다 전)</t>
+          <t>그보다 전 (작은 글씨 {t1} 이전)</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 어제 저녁 · 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
+          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -55308,6 +55330,84 @@
       <c r="P11" s="27" t="n"/>
       <c r="Q11" s="27" t="n"/>
       <c r="R11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>식사 시각 단계 (축 아님 · 이어 묻기)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>어제 저녁을 먹은 시각의 대략 범위</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁은 몇 시쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>7시 이전</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>7시~8시</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>8시 이후</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>어제 저녁(00~10시 진입). 조건은 위와 같음. 어젯밤 이미 답했으면 다시 묻지 않음</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>일상안정(최근 7일 식후 행동) 입력</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>저녁 7시 · 8시 정각 고정. 점수 · 등급 없음. 회전 후보 아님</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>DIET-Q-10</t>
+        </is>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="M12" s="27" t="inlineStr">
+        <is>
+          <t>before_7</t>
+        </is>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>seven_to_eight</t>
+        </is>
+      </c>
+      <c r="O12" s="27" t="inlineStr">
+        <is>
+          <t>after_8</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55324,7 +55424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57587,6 +57687,120 @@
       <c r="H62" s="18" t="inlineStr">
         <is>
           <t>관찰 시간 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_BOUND</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>첫 경계</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_BOUND</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>둘째 경계</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_END</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>「8시 이후」 범위 끝</t>
         </is>
       </c>
     </row>
@@ -57605,7 +57819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60315,6 +60529,38 @@
         </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁 고정 경계</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>19:00 · 20:00 · 끝 22:00</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁 선택지 「7시 이전 / 7시~8시 / 8시 이후」</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 전 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55196,12 +55196,12 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 이내 (작은 글씨 {t0} 이후)</t>
+          <t>1시간 전 (작은 글씨 {t0} 이후)</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>1~2시간 전 (작은 글씨 {t1}~{t0})</t>
+          <t>2시간 전 (작은 글씨 {t1}~{t0})</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3056,6 +3056,28 @@
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>저녁 선택지 (10-14)</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>저녁 9시 뒤 · 이른 저녁이 선택지에 안 들어갔음</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>축정의 12행 저녁 9시 뒤 고정 선택지(DIET-Q-11) 추가, 11행 어제 저녁 선택지를 「7시 이전 / 7시~9시 / 9시 이후」로, 설정값 CFG-077 · 089 · 090</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>축정의 · 설정값 · 설정파라미터</t>
         </is>
@@ -54399,7 +54421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -55196,22 +55218,22 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 전 (작은 글씨 {t0} 이후)</t>
+          <t>1시간 전</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>2시간 전 (작은 글씨 {t1}~{t0})</t>
+          <t>2시간 전</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>그보다 전 (작은 글씨 {t1} 이전)</t>
+          <t>그보다 전</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
+          <t>오늘 점심 · 오늘 저녁(오후 9시까지 답할 때). 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -55221,7 +55243,7 @@
       </c>
       <c r="J10" s="28" t="inlineStr">
         <is>
-          <t>버튼은 답한 시각(10분 내림)에서 1시간씩 거꾸로. 점심 14시 · 저녁 21시를 넘으면 멈춤. 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>시각 구간은 답한 시각(10분 내림)에서 1시간씩 거꾸로(저장용). 점심은 오후 2시가 지나면 2시에 답한 것과 같은 선택지. 하한 점심 12시 · 저녁 4시. 점수 · 등급 없음</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
@@ -55357,12 +55379,12 @@
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>7시~8시</t>
+          <t>7시~9시</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>8시 이후</t>
+          <t>9시 이후</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
@@ -55377,7 +55399,7 @@
       </c>
       <c r="J12" s="28" t="inlineStr">
         <is>
-          <t>저녁 7시 · 8시 정각 고정. 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>저녁 7시 · 9시 정각 고정(범위 17~19 · 19~21 · 21~23시). 점수 · 등급 없음</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
@@ -55397,17 +55419,95 @@
       </c>
       <c r="N12" s="27" t="inlineStr">
         <is>
-          <t>seven_to_eight</t>
+          <t>seven_to_nine</t>
         </is>
       </c>
       <c r="O12" s="27" t="inlineStr">
         <is>
-          <t>after_8</t>
+          <t>after_9</t>
         </is>
       </c>
       <c r="P12" s="27" t="n"/>
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>식사 시각 단계 (축 아님 · 이어 묻기)</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>저녁을 먹은 시각의 대략 범위(오후 9시 뒤에 답할 때)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>저녁은 몇 시쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>7시 이전</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>7시~9시</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>9시 이후</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>오늘 저녁을 오후 9시가 지나서 답할 때. 조건은 위와 같음</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>자기돌봄 · 일상안정의 식후 행동 판정 입력</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>1시간 칸 3개로는 5시 · 10시 식사를 다 덮을 수 없어 늦게 답한 날은 2시간 칸. 어제 저녁과 같은 선택지</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>DIET-Q-11</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="M13" s="27" t="inlineStr">
+        <is>
+          <t>before_7</t>
+        </is>
+      </c>
+      <c r="N13" s="27" t="inlineStr">
+        <is>
+          <t>seven_to_nine</t>
+        </is>
+      </c>
+      <c r="O13" s="27" t="inlineStr">
+        <is>
+          <t>after_9</t>
+        </is>
+      </c>
+      <c r="P13" s="27" t="n"/>
+      <c r="Q13" s="27" t="n"/>
+      <c r="R13" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55424,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57163,7 +57263,7 @@
       <c r="D48" s="18" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -57698,7 +57798,7 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_BOUND</t>
+          <t>DINNER_FIXED_BOUND</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
@@ -57736,7 +57836,7 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_BOUND</t>
+          <t>DINNER_FIXED_BOUND</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -57747,7 +57847,7 @@
       <c r="D64" s="18" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
@@ -57774,7 +57874,7 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_END</t>
+          <t>DINNER_FIXED_END</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -57785,7 +57885,7 @@
       <c r="D65" s="18" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -57801,6 +57901,82 @@
       <c r="H65" s="18" t="inlineStr">
         <is>
           <t>「8시 이후」 범위 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_TIME_FLOOR</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>DINNER 선택지 하한</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_TIME_FLOOR</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>LUNCH 선택지 하한</t>
         </is>
       </c>
     </row>
@@ -57819,7 +57995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60168,7 +60344,7 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>아침 06:00 · 점심 11:00 · 저녁 17:00</t>
+          <t>아침 06:00 · 점심 11:00 · 저녁 16:00</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
@@ -60547,20 +60723,52 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>어제 저녁 고정 경계</t>
+          <t>저녁 고정 선택지 경계</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>19:00 · 20:00 · 끝 22:00</t>
+          <t>19:00 · 21:00 · 끝 23:00</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>어제 저녁 선택지 「7시 이전 / 7시~8시 / 8시 이후」</t>
+          <t>저녁 9시 뒤 · 어제 저녁 선택지 「7시 이전 / 7시~9시 / 9시 이후」</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>선택지 하한 시각 · 저녁</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>저녁 선택지 구간이 4시 아래로 내려가지 않음(점심은 12시)</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -55524,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57977,6 +57977,44 @@
       <c r="H67" s="18" t="inlineStr">
         <is>
           <t>LUNCH 선택지 하한</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>CFG-078</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>BREAKFAST_END</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>「8시 이후」 범위 끝(아침 끝 기본값)</t>
         </is>
       </c>
     </row>
@@ -60376,12 +60414,12 @@
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>07:00 · 08:00</t>
+          <t>07:00 · 08:00 · 끝 10:00</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>아침 버튼 「7시 이전 / 7시~8시 / 8시 이후」</t>
+          <t>아침 선택지 「7시 이전 / 7시~8시 / 8시 이후」. 「8시 이후」는 10:00까지</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 전 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 이내 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55218,7 +55218,7 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 전</t>
+          <t>1시간 이내</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 이내 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55223,7 +55223,7 @@
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>2시간 전</t>
+          <t>1~2시간 전</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -55524,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57462,7 +57462,7 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>넘으면 걸음 단서 없을 때 UNKNOWN</t>
+          <t>「…이후」 칸은 끼니 끝 기본값(CFG-091)까지로 보므로 보통 넘지 않음. 넘으면 2시간까지만 봄</t>
         </is>
       </c>
     </row>
@@ -58015,6 +58015,120 @@
       <c r="H68" s="18" t="inlineStr">
         <is>
           <t>「8시 이후」 범위 끝(아침 끝 기본값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>BREAKFAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>DINNER</t>
         </is>
       </c>
     </row>
@@ -58033,7 +58147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60515,7 +60629,7 @@
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>범위가 이보다 넓거나 비어 있으면 걸음 단서가 없을 때 모름</t>
+          <t>「…이후」 칸은 끼니 끝 기본값(CFG-091)까지로 봄. 비어 있으면 모름</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
@@ -60807,6 +60921,38 @@
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>끼니 끝 기본값</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>아침 10:00 · 점심 14:00 · 저녁 23:00</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>끝이 없는 「…이후」 칸의 범위 끝</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3080,6 +3080,28 @@
       <c r="D57" s="26" t="inlineStr">
         <is>
           <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>식사 시각 추정 단순화 (10-14)</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>추정 순서에 걸음 멈춤 단서(CFG-079)와 지난 2주 평소 시각(CFG-080)이 있었음</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>둘 다 1차에서 뺌. 추정은 건강 앱 식사 기록 → 선택지 범위의 가운데 두 단계. 건강 앱 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 시각이 믿을 만하지 않음. 식후 걸음 판정 결과(모의 87~89%)는 그대로</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
         </is>
       </c>
     </row>
@@ -57390,7 +57412,7 @@
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>걸음 멈춤 단서</t>
+          <t>사용 안 함(1차)</t>
         </is>
       </c>
     </row>
@@ -57426,7 +57448,7 @@
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>평소 식사 시각</t>
+          <t>사용 안 함(1차)</t>
         </is>
       </c>
     </row>
@@ -60560,12 +60582,12 @@
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>15분</t>
+          <t>사용 안 함</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>범위 안에서 걷다가 15분 넘게 멈춘 곳이 하나뿐이면 그 시각(확신 높음). 임시값</t>
+          <t>1차에서 쓰지 않음. 건강 앱 식사 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 걸음 멈춤 단서으로 믿을 만한 시각이 나오지 않음. 추정은 건강 앱 기록 → 선택지 범위의 가운데 두 단계</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
@@ -60592,12 +60614,12 @@
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>14일</t>
+          <t>사용 안 함</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>지난 14일 같은 끼니의 추정 시각 중앙값. 임시값</t>
+          <t>1차에서 쓰지 않음. 건강 앱 식사 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 식사 시각으로 믿을 만한 시각이 나오지 않음. 추정은 건강 앱 기록 → 선택지 범위의 가운데 두 단계</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -60459,7 +60459,7 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>14시를 넘으면 「오후 1:00 이후 / 12:00~1:00 / 12:00 이전」</t>
+          <t>14시를 넘으면 「오후 1시 이후 / 12시~1시 사이 / 12시 이전」</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -60459,7 +60459,7 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>14시를 넘으면 「오후 1시 이후 / 12시~1시 사이 / 12시 이전」</t>
+          <t>14시를 넘으면 「1시 이후 / 12시~1시 사이 / 12시 이전」</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>오늘도 어제와 비슷한 시간에 아침·점심·저녁 세 끼를 드세요.</t>
+          <t>오늘도 아침·점심·저녁 세 끼를 제때 드세요.</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -22560,20 +22560,20 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>세 끼 어제처럼 먹기</t>
+          <t>세 끼 제때 먹기</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>오늘도 어제와 비슷한 시간에 아침·점심·저녁 세 끼를 드세요.</t>
+          <t>오늘도 아침·점심·저녁 세 끼를 제때 드세요.</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>식사 시각을 일정하게 계획해 보는 행동이에요.</t>
+          <t>세 끼를 제때 먹도록 계획해 보는 행동이에요.</t>
         </is>
       </c>
       <c r="K5" s="13" t="n"/>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P5" s="13" t="inlineStr">
@@ -24292,11 +24292,11 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>다음 끼니는 챙기기</t>
+          <t>다음 끼니 잘 챙기기</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -25764,20 +25764,20 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>라면 국물은 남기기</t>
+          <t>국물 음식은 국물 남기기</t>
         </is>
       </c>
       <c r="H45" s="13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>라면을 먹을 때 면과 건더기만 먹고 국물은 남기세요.</t>
+          <t>국이나 면 같은 국물 음식은 건더기만 먹고 국물은 남기세요.</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>라면 국물을 남겨 국물 섭취를 줄여요.</t>
+          <t>국물을 남겨 국물 섭취를 줄여요.</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -25928,20 +25928,20 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>김치는 먹을 만큼만</t>
+          <t>절임 반찬은 먹을 만큼만</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>김치는 먹을 만큼만 조금 덜어서 드세요.</t>
+          <t>김치·장아찌 같은 절임 반찬은 먹을 만큼만 조금 덜어서 드세요.</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>김치의 양과 다른 짠 반찬을 함께 살펴봐요.</t>
+          <t>절임 반찬의 양과 다른 짠 반찬을 함께 살펴봐요.</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -27004,15 +27004,15 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>라면 대신 국수 · 밥</t>
+          <t>튀긴 면 대신 국수 · 밥</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>라면이 당길 때 기름에 튀기지 않은 국수나 밥으로 바꿔 드세요.</t>
+          <t>기름에 튀긴 면이 당길 때 튀기지 않은 국수나 밥으로 바꿔 드세요.</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P60" s="13" t="inlineStr">
@@ -28248,20 +28248,20 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>김치는 접시에 덜기</t>
+          <t>절임 반찬은 접시에 덜기</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>김치는 통째로 두지 말고 먹을 만큼 앞접시에 덜어 드세요.</t>
+          <t>김치 같은 절임 반찬은 통째로 두지 말고 먹을 만큼 앞접시에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J75" s="14" t="inlineStr">
         <is>
-          <t>김치의 실제 양과 전체 식사의 간을 함께 봐요.</t>
+          <t>절임 반찬의 실제 양과 전체 식사의 간을 함께 봐요.</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="O75" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P75" s="13" t="inlineStr">
@@ -28332,20 +28332,20 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>저녁 어제처럼 먹기</t>
+          <t>저녁은 제때 먹기</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>오늘 저녁도 어제와 비슷한 시간에 드세요.</t>
+          <t>오늘 저녁도 제때 드세요.</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>생활 일정에 맞춰 저녁 시각을 계획해요.</t>
+          <t>저녁을 제때 먹도록 계획해요.</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="O76" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P76" s="13" t="inlineStr">
@@ -28412,11 +28412,11 @@
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>한 숟갈 양을 절반으로</t>
+          <t>한 숟갈 양, 절반만</t>
         </is>
       </c>
       <c r="H77" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="O77" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
@@ -32224,20 +32224,20 @@
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>냉면 국물은 반만</t>
+          <t>면 국물은 반만</t>
         </is>
       </c>
       <c r="H123" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>냉면을 먹을 때 국물은 절반만 드세요.</t>
+          <t>면 요리를 먹을 때 국물은 절반만 드세요.</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>냉면 국물의 섭취량을 줄여 봐요.</t>
+          <t>면 국물의 섭취량을 줄여 봐요.</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="O123" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P123" s="13" t="inlineStr">
@@ -36092,11 +36092,11 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>오징어·새우로 한 끼</t>
+          <t>해산물로 한 끼</t>
         </is>
       </c>
       <c r="H171" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P171" s="8" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 두부조림</t>
+          <t>내일 반찬은 두부 요리</t>
         </is>
       </c>
       <c r="H191" s="8">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 두부조림을 준비해 보세요.</t>
+          <t>내일 반찬으로 두부조림이나 두부부침을 준비해 보세요.</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>두부조림은 손쉬운 단백질 반찬이에요.</t>
+          <t>두부 반찬은 손쉬운 단백질 반찬이에요.</t>
         </is>
       </c>
       <c r="K191" s="8" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 14번)</t>
+          <t>10-13 추가(검수표 14번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P191" s="8" t="inlineStr">
@@ -37815,7 +37815,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 고등어구이</t>
+          <t>내일 반찬은 생선구이</t>
         </is>
       </c>
       <c r="H193" s="8">
@@ -37824,12 +37824,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 튀김 대신 고등어구이를 준비해 보세요.</t>
+          <t>내일 반찬으로 튀김 대신 고등어 같은 생선구이를 준비해 보세요.</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>고등어구이는 튀김보다 기름이 덜 들어가요.</t>
+          <t>생선구이는 튀김보다 기름이 덜 들어가요.</t>
         </is>
       </c>
       <c r="K193" s="8" t="inlineStr">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 16번)</t>
+          <t>10-13 추가(검수표 16번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P193" s="8" t="inlineStr">
@@ -38131,7 +38131,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>내일은 죽 한 그릇</t>
+          <t>내일은 부드러운 한 끼</t>
         </is>
       </c>
       <c r="H197" s="8">
@@ -38140,12 +38140,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>입맛이 없다면 내일 한 끼는 죽 한 그릇으로 드세요.</t>
+          <t>입맛이 없다면 내일 한 끼는 죽처럼 부드러운 음식으로 드세요.</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>죽은 입맛이 없을 때도 먹기 편해요.</t>
+          <t>부드러운 음식은 입맛이 없을 때도 먹기 편해요.</t>
         </is>
       </c>
       <c r="K197" s="8" t="inlineStr">
@@ -38166,7 +38166,7 @@
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 20번)</t>
+          <t>10-13 추가(검수표 20번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P197" s="8" t="inlineStr">
@@ -39144,7 +39144,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>점심엔 닭가슴살 샐러드</t>
+          <t>점심엔 단백질 샐러드</t>
         </is>
       </c>
       <c r="H210" s="8">
@@ -39153,12 +39153,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>내일 점심은 닭가슴살을 올린 샐러드로 드세요.</t>
+          <t>내일 점심은 닭가슴살이나 달걀을 올린 샐러드로 드세요.</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>닭가슴살 샐러드는 단백질과 채소를 함께 챙겨요.</t>
+          <t>단백질 샐러드는 단백질과 채소를 함께 챙겨요.</t>
         </is>
       </c>
       <c r="K210" s="8" t="inlineStr">
@@ -39175,7 +39175,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 33번)</t>
+          <t>10-13 추가(검수표 33번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P210" s="8" t="inlineStr">
@@ -39691,7 +39691,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>바쁜 날엔 김밥 한 줄</t>
+          <t>바쁜 날엔 간단한 한 끼</t>
         </is>
       </c>
       <c r="H217" s="8">
@@ -39700,12 +39700,12 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>바빠서 밥 먹을 시간이 없는 날엔 김밥 한 줄이라도 드세요.</t>
+          <t>바빠서 밥 먹을 시간이 없는 날엔 김밥 한 줄처럼 간단한 한 끼라도 드세요.</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>바쁜 날에도 김밥 한 줄이면 끼니를 챙겨요.</t>
+          <t>바쁜 날에도 간단한 한 끼면 끼니를 챙겨요.</t>
         </is>
       </c>
       <c r="K217" s="8" t="inlineStr">
@@ -39722,7 +39722,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 40번)</t>
+          <t>10-13 추가(검수표 40번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P217" s="8" t="inlineStr">
@@ -39845,7 +39845,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>내일 된장국에 애호박</t>
+          <t>내일 국엔 호박 · 버섯</t>
         </is>
       </c>
       <c r="H219" s="8">
@@ -39854,12 +39854,12 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>내일 된장국을 끓일 때 애호박을 넣어 보세요.</t>
+          <t>내일 국을 끓일 때 애호박이나 버섯을 넣어 보세요.</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>애호박을 넣으면 국 한 그릇에 채소가 더해져요.</t>
+          <t>채소를 넣으면 국 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K219" s="8" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 42번)</t>
+          <t>10-13 추가(검수표 42번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P219" s="8" t="inlineStr">
@@ -41320,7 +41320,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>돼지갈비 대신 생선찜</t>
+          <t>양념 고기 대신 생선찜</t>
         </is>
       </c>
       <c r="H238" s="8">
@@ -41329,7 +41329,7 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>돼지갈비 대신 생선찜을 골라 드세요.</t>
+          <t>양념한 고기구이 대신 생선찜을 골라 드세요.</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
@@ -41355,7 +41355,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 61번)</t>
+          <t>10-13 추가(검수표 61번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P238" s="8" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>라면에 채소 넣기</t>
+          <t>면 요리에 채소 넣기</t>
         </is>
       </c>
       <c r="H248" s="8">
@@ -42107,7 +42107,7 @@
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 파·양배추 같은 채소를 넣어 드세요.</t>
+          <t>면을 끓일 때 파·양배추 같은 채소를 넣어 드세요.</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
@@ -42133,7 +42133,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 71번)</t>
+          <t>10-13 추가(검수표 71번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr">
@@ -42179,7 +42179,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>채소 많은 김밥 고르기</t>
+          <t>채소 많은 메뉴 고르기</t>
         </is>
       </c>
       <c r="H249" s="8">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>김밥을 고를 때 채소가 많이 들어간 것으로 고르세요.</t>
+          <t>김밥이나 도시락을 고를 때 채소가 많이 들어간 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 72번)</t>
+          <t>10-13 추가(검수표 72번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P249" s="8" t="inlineStr">
@@ -43277,7 +43277,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>내일은 맑은 콩나물국</t>
+          <t>내일은 맑은 국으로</t>
         </is>
       </c>
       <c r="H263" s="8">
@@ -43286,12 +43286,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>내일 국은 찌개 대신 맑은 콩나물국으로 끓여 보세요.</t>
+          <t>내일 국은 찌개 대신 콩나물국처럼 맑은 국으로 끓여 보세요.</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>맑은 콩나물국은 찌개보다 덜 짜요.</t>
+          <t>맑은 국은 찌개보다 덜 짜요.</t>
         </is>
       </c>
       <c r="K263" s="8" t="inlineStr">
@@ -43308,7 +43308,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 86번)</t>
+          <t>10-13 추가(검수표 86번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P263" s="8" t="inlineStr">
@@ -44845,7 +44845,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>삼겹살 대신 보쌈</t>
+          <t>구운 고기 대신 삶은 고기</t>
         </is>
       </c>
       <c r="H283" s="8">
@@ -44854,12 +44854,12 @@
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>구운 삼겹살 대신 삶은 보쌈을 골라 드세요.</t>
+          <t>기름에 구운 고기 대신 보쌈처럼 삶은 고기를 골라 드세요.</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>삶은 고기는 구운 삼겹살보다 기름이 덜해요.</t>
+          <t>삶은 고기는 구운 고기보다 기름이 덜해요.</t>
         </is>
       </c>
       <c r="K283" s="8" t="inlineStr">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 106번)</t>
+          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P283" s="8" t="inlineStr">
@@ -44926,7 +44926,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>잡채 대신 나물무침</t>
+          <t>볶은 반찬 대신 나물무침</t>
         </is>
       </c>
       <c r="H284" s="8">
@@ -44935,12 +44935,12 @@
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>기름에 볶은 잡채 대신 나물무침을 골라 드세요.</t>
+          <t>기름에 볶은 반찬 대신 나물무침을 골라 드세요.</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>나물무침은 잡채보다 기름을 덜 써요.</t>
+          <t>나물무침은 볶은 반찬보다 기름을 덜 써요.</t>
         </is>
       </c>
       <c r="K284" s="8" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 107번)</t>
+          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P284" s="8" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 콩나물무침</t>
+          <t>내일 반찬은 나물무침</t>
         </is>
       </c>
       <c r="H287" s="8">
@@ -45174,12 +45174,12 @@
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 콩나물무침을 준비해 보세요.</t>
+          <t>내일 반찬으로 콩나물무침 같은 나물무침을 준비해 보세요.</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>콩나물무침은 기름을 거의 쓰지 않아요.</t>
+          <t>나물무침은 기름을 거의 쓰지 않아요.</t>
         </is>
       </c>
       <c r="K287" s="8" t="inlineStr">
@@ -45196,7 +45196,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 110번)</t>
+          <t>10-13 추가(검수표 110번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P287" s="8" t="inlineStr">
@@ -45242,7 +45242,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>제육볶음 대신 수육</t>
+          <t>볶은 고기 대신 수육</t>
         </is>
       </c>
       <c r="H288" s="8">
@@ -45251,7 +45251,7 @@
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>제육볶음 대신 삶은 수육을 골라 드세요.</t>
+          <t>양념해 볶은 고기 대신 삶은 수육을 골라 드세요.</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 111번)</t>
+          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P288" s="8" t="inlineStr">
@@ -45323,7 +45323,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>돈가스 대신 생선구이</t>
+          <t>튀긴 고기 대신 생선구이</t>
         </is>
       </c>
       <c r="H289" s="8">
@@ -45332,12 +45332,12 @@
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>돈가스 대신 생선구이를 골라 드세요.</t>
+          <t>튀긴 고기 요리 대신 생선구이를 골라 드세요.</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>생선구이는 돈가스보다 기름이 덜 들어가요.</t>
+          <t>생선구이는 튀긴 고기보다 기름이 덜 들어가요.</t>
         </is>
       </c>
       <c r="K289" s="8" t="inlineStr">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 112번)</t>
+          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P289" s="8" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>치킨 대신 닭백숙</t>
+          <t>튀긴 닭 대신 삶은 닭</t>
         </is>
       </c>
       <c r="H290" s="8">
@@ -45413,7 +45413,7 @@
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>튀긴 치킨 대신 삶은 닭백숙을 드세요.</t>
+          <t>튀긴 닭 대신 백숙처럼 삶은 닭을 드세요.</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 113번)</t>
+          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P290" s="8" t="inlineStr">
@@ -45485,7 +45485,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>김치찌개 대신 맑은 국</t>
+          <t>찌개 대신 맑은 국</t>
         </is>
       </c>
       <c r="H291" s="8">
@@ -45494,7 +45494,7 @@
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>김치찌개 대신 맑게 끓인 국을 골라 드세요.</t>
+          <t>짭짤한 찌개 대신 맑게 끓인 국을 골라 드세요.</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 114번)</t>
+          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P291" s="8" t="inlineStr">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>믹스 대신 블랙커피</t>
+          <t>단 커피 대신 블랙커피</t>
         </is>
       </c>
       <c r="H292" s="8">
@@ -45571,12 +45571,12 @@
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>믹스커피 대신 설탕 없는 블랙커피를 드세요.</t>
+          <t>설탕 든 커피 대신 설탕 없는 블랙커피를 드세요.</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>아메리카노에는 설탕이 들어 있지 않아요.</t>
+          <t>블랙커피에는 설탕이 들어 있지 않아요.</t>
         </is>
       </c>
       <c r="K292" s="8" t="inlineStr">
@@ -45593,7 +45593,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 115번)</t>
+          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P292" s="8" t="inlineStr">
@@ -45639,7 +45639,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>케이크 대신 요거트</t>
+          <t>단 디저트 대신 요거트</t>
         </is>
       </c>
       <c r="H293" s="8">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>케이크 대신 달지 않은 플레인 요거트를 드세요.</t>
+          <t>케이크 같은 단 디저트 대신 달지 않은 플레인 요거트를 드세요.</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 116번)</t>
+          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P293" s="8" t="inlineStr">
@@ -45716,7 +45716,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>짜장면 대신 비빔밥</t>
+          <t>기름진 면 대신 나물밥</t>
         </is>
       </c>
       <c r="H294" s="8">
@@ -45725,12 +45725,12 @@
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>짜장면 대신 나물이 들어간 비빔밥을 골라 드세요.</t>
+          <t>기름진 면 요리 대신 나물이 들어간 밥을 골라 드세요.</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>비빔밥은 채소를 넉넉히 먹을 수 있어요.</t>
+          <t>나물밥은 채소를 넉넉히 먹을 수 있어요.</t>
         </is>
       </c>
       <c r="K294" s="8" t="inlineStr">
@@ -45747,7 +45747,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 117번)</t>
+          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P294" s="8" t="inlineStr">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>아침엔 누룽지 한 그릇</t>
+          <t>아침엔 따뜻한 한 그릇</t>
         </is>
       </c>
       <c r="H296" s="8">
@@ -45883,12 +45883,12 @@
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>아침에 따뜻한 누룽지 한 그릇으로 식사를 챙겨 보세요.</t>
+          <t>아침에 누룽지나 죽처럼 따뜻한 한 그릇으로 식사를 챙겨 보세요.</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>따뜻한 누룽지는 아침에 부담 없이 먹기 좋아요.</t>
+          <t>따뜻한 한 그릇은 아침에 부담 없이 먹기 좋아요.</t>
         </is>
       </c>
       <c r="K296" s="8" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 119번)</t>
+          <t>10-13 추가(검수표 119번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P296" s="8" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>라면엔 콩나물 한 줌</t>
+          <t>면 요리에 콩나물 한 줌</t>
         </is>
       </c>
       <c r="H298" s="8">
@@ -46037,12 +46037,12 @@
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 콩나물을 한 줌 넣어 드세요.</t>
+          <t>면을 끓일 때 콩나물이나 숙주를 한 줌 넣어 드세요.</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 라면에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 면 요리에도 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K298" s="8" t="inlineStr">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 121번)</t>
+          <t>10-13 추가(검수표 121번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P298" s="8" t="inlineStr">
@@ -46109,7 +46109,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>비빔밥은 나물 듬뿍</t>
+          <t>밥엔 나물 듬뿍</t>
         </is>
       </c>
       <c r="H299" s="8">
@@ -46118,7 +46118,7 @@
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>비빔밥을 먹을 때 나물을 듬뿍 넣어 드세요.</t>
+          <t>밥을 먹을 때 나물을 듬뿍 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
@@ -46144,7 +46144,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 122번)</t>
+          <t>10-13 추가(검수표 122번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P299" s="8" t="inlineStr">
@@ -46190,7 +46190,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>달걀말이에 부추 넣기</t>
+          <t>달걀 요리에 채소 넣기</t>
         </is>
       </c>
       <c r="H300" s="8">
@@ -46199,12 +46199,12 @@
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>달걀말이를 만들 때 부추를 썰어 넣어 보세요.</t>
+          <t>달걀말이나 달걀찜을 만들 때 부추·파 같은 채소를 넣어 보세요.</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>부추를 넣으면 반찬 하나에 채소가 더해져요.</t>
+          <t>채소를 넣으면 반찬 하나에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K300" s="8" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 123번)</t>
+          <t>10-13 추가(검수표 123번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P300" s="8" t="inlineStr">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>라면에 달걀 하나</t>
+          <t>면 요리에 달걀 하나</t>
         </is>
       </c>
       <c r="H301" s="8">
@@ -46280,12 +46280,12 @@
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 달걀을 하나 넣어 드세요.</t>
+          <t>면을 끓일 때 달걀을 하나 넣어 드세요.</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 라면에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 면 요리에도 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="K301" s="8" t="inlineStr">
@@ -46306,7 +46306,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 124번)</t>
+          <t>10-13 추가(검수표 124번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P301" s="8" t="inlineStr">
@@ -46352,7 +46352,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>김밥은 참치·계란으로</t>
+          <t>간편식엔 참치·달걀</t>
         </is>
       </c>
       <c r="H302" s="8">
@@ -46361,12 +46361,12 @@
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>김밥을 고를 때 참치나 계란이 든 김밥으로 고르세요.</t>
+          <t>김밥 같은 간편식을 고를 때 참치나 달걀이 든 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>참치·계란 김밥으로 단백질을 챙겨요.</t>
+          <t>참치나 달걀이 든 간편식으로 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="K302" s="8" t="inlineStr">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 125번)</t>
+          <t>10-13 추가(검수표 125번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P302" s="8" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>식혜 대신 보리차</t>
+          <t>단 음료 대신 보리차</t>
         </is>
       </c>
       <c r="H304" s="8">
@@ -46515,7 +46515,7 @@
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>식혜 대신 달지 않은 보리차를 드세요.</t>
+          <t>식혜 같은 단 음료 대신 달지 않은 보리차를 드세요.</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 127번)</t>
+          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P304" s="8" t="inlineStr">
@@ -46587,7 +46587,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>라떼는 시럽 빼고</t>
+          <t>주문할 땐 시럽 빼고</t>
         </is>
       </c>
       <c r="H305" s="8">
@@ -46596,12 +46596,12 @@
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>라떼를 주문할 때 시럽은 빼 달라고 하세요.</t>
+          <t>음료를 주문할 때 시럽은 빼 달라고 하세요.</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>시럽을 빼면 라떼의 당이 크게 줄어요.</t>
+          <t>시럽을 빼면 음료의 당이 크게 줄어요.</t>
         </is>
       </c>
       <c r="K305" s="8" t="inlineStr">
@@ -46618,7 +46618,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 128번)</t>
+          <t>10-13 추가(검수표 128번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P305" s="8" t="inlineStr">
@@ -46664,7 +46664,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>믹스커피는 반 봉지만</t>
+          <t>커피 설탕은 반만</t>
         </is>
       </c>
       <c r="H306" s="8">
@@ -46673,12 +46673,12 @@
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>믹스커피를 탈 때 한 봉지 대신 반 봉지만 넣으세요.</t>
+          <t>커피에 넣는 설탕이나 믹스는 평소의 절반만 넣으세요.</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>반 봉지만 타도 단맛은 충분해요.</t>
+          <t>설탕을 반만 넣어도 단맛은 충분해요.</t>
         </is>
       </c>
       <c r="K306" s="8" t="inlineStr">
@@ -46699,7 +46699,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 129번)</t>
+          <t>10-13 추가(검수표 129번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P306" s="8" t="inlineStr">
@@ -46745,7 +46745,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>라면 스프는 반만</t>
+          <t>분말 스프는 반만</t>
         </is>
       </c>
       <c r="H307" s="8">
@@ -46754,7 +46754,7 @@
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 스프는 절반만 넣으세요.</t>
+          <t>면이나 즉석 국에 든 분말 스프는 절반만 넣으세요.</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
@@ -46780,7 +46780,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 130번)</t>
+          <t>10-13 추가(검수표 130번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P307" s="8" t="inlineStr">
@@ -46826,7 +46826,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>김치는 백김치로</t>
+          <t>절임 반찬은 덜 짠 것으로</t>
         </is>
       </c>
       <c r="H308" s="8">
@@ -46835,12 +46835,12 @@
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>빨간 김치 대신 백김치를 곁들여 드세요.</t>
+          <t>김치나 장아찌는 백김치처럼 덜 짠 것으로 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>백김치는 빨간 김치보다 덜 짠 편이에요.</t>
+          <t>덜 짠 절임 반찬을 고르면 나트륨이 줄어요.</t>
         </is>
       </c>
       <c r="K308" s="8" t="inlineStr">
@@ -46857,7 +46857,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 131번)</t>
+          <t>10-13 추가(검수표 131번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P308" s="8" t="inlineStr">
@@ -46903,7 +46903,7 @@
       </c>
       <c r="G309" s="8" t="inlineStr">
         <is>
-          <t>오징어튀김 대신 숙회</t>
+          <t>해물 튀김 대신 숙회</t>
         </is>
       </c>
       <c r="H309" s="8">
@@ -46912,7 +46912,7 @@
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>오징어튀김 대신 데친 오징어 숙회를 드세요.</t>
+          <t>해물 튀김 대신 데친 숙회를 드세요.</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
@@ -46938,7 +46938,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 132번)</t>
+          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P309" s="8" t="inlineStr">
@@ -46984,7 +46984,7 @@
       </c>
       <c r="G310" s="8" t="inlineStr">
         <is>
-          <t>치킨은 오븐구이로</t>
+          <t>닭은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="H310" s="8">
@@ -46993,12 +46993,12 @@
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>치킨은 튀긴 것 대신 오븐에 구운 것으로 고르세요.</t>
+          <t>닭 요리는 튀긴 것 대신 오븐에 구운 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>오븐구이는 튀긴 치킨보다 기름이 덜해요.</t>
+          <t>오븐구이는 튀긴 닭보다 기름이 덜해요.</t>
         </is>
       </c>
       <c r="K310" s="8" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 133번)</t>
+          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P310" s="8" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -31308,15 +31308,15 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>혼자여도 상 차려 먹기</t>
+          <t>대충 때우지 않고 차려 먹기</t>
         </is>
       </c>
       <c r="H112" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>혼자 먹더라도 대충 때우지 말고 상을 차려서 드세요.</t>
+          <t>간단히 먹더라도 대충 때우지 말고 상을 차려서 드세요.</t>
         </is>
       </c>
       <c r="J112" s="14" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="O112" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P112" s="13" t="inlineStr">
@@ -31388,15 +31388,15 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>혼밥도 그릇에 덜기</t>
+          <t>봉지째 말고 그릇에 덜기</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 봉지째 먹지 말고 그릇에 덜어 드세요.</t>
+          <t>봉지째 먹지 말고 그릇에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="O113" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P113" s="13" t="inlineStr">
@@ -31472,20 +31472,20 @@
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>혼밥에도 채소 한 가지</t>
+          <t>간단히 먹어도 채소 하나</t>
         </is>
       </c>
       <c r="H114" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 채소 반찬을 한 가지 곁들여 드세요.</t>
+          <t>간단히 먹을 때도 채소 반찬을 한 가지 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 채소 반찬을 준비해 봐요.</t>
+          <t>간단한 식사에도 채소 반찬을 준비해 봐요.</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="O114" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P114" s="13" t="inlineStr">
@@ -31556,15 +31556,15 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>혼밥에도 단백질 챙기기</t>
+          <t>간단히 먹어도 단백질</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>혼자 간단히 먹을 때도 달걀·두부 같은 단백질 식품을 곁들이세요.</t>
+          <t>간단히 먹을 때도 달걀·두부 같은 단백질 식품을 곁들이세요.</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="O115" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P115" s="13" t="inlineStr">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>도시락에 채소 한 칸</t>
+          <t>채소 반찬 미리 담기</t>
         </is>
       </c>
       <c r="H116" s="13" t="n">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>도시락을 쌀 때 한 칸은 채소 반찬으로 채우세요.</t>
+          <t>내일 먹을 채소 반찬을 미리 한 칸 담아 두세요.</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="O116" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P116" s="13" t="inlineStr">
@@ -31724,15 +31724,15 @@
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>도시락에 달걀 하나</t>
+          <t>달걀 반찬 하나 챙기기</t>
         </is>
       </c>
       <c r="H117" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>도시락에 달걀 반찬을 하나 넣어 가세요.</t>
+          <t>달걀 반찬을 하나 챙겨 드세요.</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="O117" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P117" s="13" t="inlineStr">
@@ -31808,15 +31808,15 @@
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>도시락 국물은 빼기</t>
+          <t>국물 반찬은 빼고 담기</t>
         </is>
       </c>
       <c r="H118" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>도시락을 쌀 때 국이나 국물 반찬은 빼고 싸세요.</t>
+          <t>반찬을 담을 때 국이나 국물 반찬은 빼고 담으세요.</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="O118" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P118" s="13" t="inlineStr">
@@ -31892,20 +31892,20 @@
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>도시락 반찬은 구이로</t>
+          <t>반찬은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="H119" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>도시락 반찬은 튀김 대신 구이로 만들어 담으세요.</t>
+          <t>반찬은 튀김 대신 구이로 만들어 드세요.</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr">
         <is>
-          <t>도시락 반찬의 조리법을 바꿔 보는 행동이에요.</t>
+          <t>반찬의 조리법을 바꿔 보는 행동이에요.</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
@@ -31926,7 +31926,7 @@
       </c>
       <c r="O119" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P119" s="13" t="inlineStr">
@@ -31976,20 +31976,20 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>가족 반찬에 채소 하나</t>
+          <t>상 차릴 때 채소 하나 더</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>가족과 함께 먹는 상에 채소 반찬을 한 가지 더 올려 보세요.</t>
+          <t>상을 차릴 때 채소 반찬을 한 가지 더 올려 보세요.</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>함께 먹는 반찬이 늘면 나도 늘어요.</t>
+          <t>상에 오르는 채소가 늘면 먹는 채소도 늘어요.</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="O120" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P120" s="13" t="inlineStr">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>국은 각자 그릇에 덜기</t>
+          <t>국은 그릇에 덜어 먹기</t>
         </is>
       </c>
       <c r="H121" s="13" t="n">
@@ -32068,12 +32068,12 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>국은 냄비째 떠먹지 말고 각자 그릇에 덜어 드세요.</t>
+          <t>국은 냄비째 떠먹지 말고 그릇에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
         <is>
-          <t>각자 덜어 실제 먹는 양을 살펴봐요.</t>
+          <t>그릇에 덜어 실제 먹는 양을 살펴봐요.</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="O121" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P121" s="13" t="inlineStr">
@@ -32224,20 +32224,20 @@
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>면 국물은 반만</t>
+          <t>국물 음식은 절반만</t>
         </is>
       </c>
       <c r="H123" s="13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>면 요리를 먹을 때 국물은 절반만 드세요.</t>
+          <t>국물 음식을 먹을 때 국물은 절반만 드세요.</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>면 국물의 섭취량을 줄여 봐요.</t>
+          <t>국물 섭취량을 줄여 봐요.</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="O123" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P123" s="13" t="inlineStr">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>함께 먹는 끼니 정하기</t>
+          <t>하루 한 끼는 여유 있게</t>
         </is>
       </c>
       <c r="H232" s="8">
@@ -40863,12 +40863,12 @@
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>가족이나 친구와 함께 먹을 끼니를 하루 한 번 정해 보세요.</t>
+          <t>하루 한 끼는 서두르지 않고 여유 있게 먹을 끼니로 정해 보세요.</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>함께 먹으면 천천히, 즐겁게 먹게 돼요.</t>
+          <t>끼니 하나를 정해 두면 천천히 즐겁게 먹게 돼요.</t>
         </is>
       </c>
       <c r="K232" s="8" t="inlineStr">
@@ -40885,7 +40885,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 55번)</t>
+          <t>10-13 추가(검수표 55번) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P232" s="8" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>면 요리에 채소 넣기</t>
+          <t>끓일 때 채소 한 줌 넣기</t>
         </is>
       </c>
       <c r="H248" s="8">
@@ -42107,7 +42107,7 @@
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>면을 끓일 때 파·양배추 같은 채소를 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 파·양배추 같은 채소를 한 줌 넣어 드세요.</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
@@ -42133,7 +42133,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 71번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 71번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr">
@@ -44764,7 +44764,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>도시락에 단백질 담기</t>
+          <t>내일 단백질 반찬 담기</t>
         </is>
       </c>
       <c r="H282" s="8">
@@ -44773,12 +44773,12 @@
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>내일 도시락에 고기·생선·달걀·두부 반찬을 한 가지 담으세요.</t>
+          <t>내일 먹을 고기·생선·달걀·두부 반찬을 한 가지 담아 두세요.</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+          <t>미리 담아 두면 밖에서도 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="K282" s="8" t="inlineStr">
@@ -44799,7 +44799,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 105번)</t>
+          <t>10-13 추가(검수표 105번) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P282" s="8" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>면 요리에 콩나물 한 줌</t>
+          <t>끓일 때 콩나물 한 줌</t>
         </is>
       </c>
       <c r="H298" s="8">
@@ -46037,12 +46037,12 @@
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>면을 끓일 때 콩나물이나 숙주를 한 줌 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 콩나물이나 숙주를 한 줌 넣어 드세요.</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 면 요리에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K298" s="8" t="inlineStr">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 121번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 121번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P298" s="8" t="inlineStr">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>면 요리에 달걀 하나</t>
+          <t>끓일 때 달걀 하나 넣기</t>
         </is>
       </c>
       <c r="H301" s="8">
@@ -46280,12 +46280,12 @@
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>면을 끓일 때 달걀을 하나 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 달걀을 하나 넣어 드세요.</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 면 요리에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 한 그릇에 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="K301" s="8" t="inlineStr">
@@ -46306,7 +46306,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 124번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 124번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P301" s="8" t="inlineStr">
@@ -46745,7 +46745,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>분말 스프는 반만</t>
+          <t>양념은 절반만 넣기</t>
         </is>
       </c>
       <c r="H307" s="8">
@@ -46754,12 +46754,12 @@
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>면이나 즉석 국에 든 분말 스프는 절반만 넣으세요.</t>
+          <t>국이나 찌개, 즉석식품의 양념은 절반만 넣으세요.</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+          <t>양념을 반만 넣으면 나트륨이 크게 줄어요.</t>
         </is>
       </c>
       <c r="K307" s="8" t="inlineStr">
@@ -46780,7 +46780,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 130번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 130번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P307" s="8" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -33040,20 +33040,20 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>마실 것 미리 정하기</t>
+          <t>오늘 마실 음료 정하기</t>
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>카페나 편의점에 가기 전에 무엇을 마실지 미리 정해 두세요.</t>
+          <t>오늘 무엇을 마실지 미리 정해 두세요. 정해 두면 카페나 편의점에서 단 음료를 충동적으로 고르는 일이 줄어요.</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
         <is>
-          <t>미리 정해 두면 고르는 순간에 헤매지 않아요.</t>
+          <t>미리 정해 두면 단 음료를 충동적으로 고르지 않게 돼요.</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="O133" s="14" t="inlineStr">
         <is>
-          <t>감량·공복·증량 금지가 걸린 사용자에게 도전 단계 후보가 0이 되던 칸을 채우려고 추가. 성격은 비워 둔다</t>
+          <t>감량·공복·증량 금지가 걸린 사용자에게 도전 단계 후보가 0이 되던 칸을 채우려고 추가. 성격은 비워 둔다 · 10-19 효과가 드러나게 다듬음</t>
         </is>
       </c>
       <c r="P133" s="13" t="inlineStr">
@@ -33680,20 +33680,20 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>내일 쓸 두부 준비하기</t>
+          <t>내일 두부 반찬 준비하기</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 쓸 두부가 냉장고에 있는지 확인하고 준비해 두세요.</t>
+          <t>내일 먹을 두부 반찬을 미리 준비해 두세요. 준비해 두면 내일 단백질 반찬을 챙기기 쉬워요.</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
         <is>
-          <t>두부를 냉장고에 두면 내일 준비할 재료를 미리 확인할 수 있어요.</t>
+          <t>준비해 두면 내일 단백질 반찬을 챙기기 쉬워요.</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="O141" s="14" t="inlineStr">
         <is>
-          <t>저녁 식사 후에도 실행 가능한 다음 날 준비 행동.</t>
+          <t>저녁 식사 후에도 실행 가능한 다음 날 준비 행동. · 10-19 효과가 드러나게 다듬음</t>
         </is>
       </c>
       <c r="P141" s="13" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -34084,20 +34084,20 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>마가린·쇼트닝 빼기</t>
+          <t>트랜스지방 없는 하루</t>
         </is>
       </c>
       <c r="H146" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>요리할 때 마가린이나 쇼트닝은 쓰지 말고 빼 보세요.</t>
+          <t>오늘 하루는 마가린·쇼트닝처럼 트랜스지방이 든 기름을 쓰지 않고 지내 보세요.</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>트랜스지방이 많은 기름을 빼는 행동이에요.</t>
+          <t>트랜스지방이 든 기름을 하루 쓰지 않는 행동이에요.</t>
         </is>
       </c>
       <c r="K146" s="8" t="inlineStr">
@@ -34114,7 +34114,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 「없는 하루」 꼴로</t>
         </is>
       </c>
       <c r="P146" s="8" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -25019,7 +25019,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P36" s="13" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P42" s="13" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P57" s="13" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="O84" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P84" s="13" t="inlineStr">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
@@ -35642,7 +35642,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P165" s="8" t="inlineStr">
@@ -37891,7 +37891,7 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 17번)</t>
+          <t>10-13 추가(검수표 17번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P194" s="8" t="inlineStr">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G202" s="8" t="inlineStr">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 25번)</t>
+          <t>10-13 추가(검수표 25번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P202" s="8" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
@@ -38636,7 +38636,7 @@
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 26번)</t>
+          <t>10-13 추가(검수표 26번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P203" s="8" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>저녁은 매일 7시쯤</t>
+          <t>저녁은 매일 같은 시간에</t>
         </is>
       </c>
       <c r="H229" s="8">
@@ -40632,7 +40632,7 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>매일 저녁 7시쯤 비슷한 시간에 저녁을 드세요.</t>
+          <t>매일 저녁을 정해진 시간에 드세요.</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
@@ -40654,7 +40654,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 52번)</t>
+          <t>10-13 추가(검수표 52번) · 10-19 특정 시각 전제 없이</t>
         </is>
       </c>
       <c r="P229" s="8" t="inlineStr">
@@ -44840,7 +44840,7 @@
       </c>
       <c r="F283" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G283" s="8" t="inlineStr">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P283" s="8" t="inlineStr">
@@ -44921,7 +44921,7 @@
       </c>
       <c r="F284" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G284" s="8" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P284" s="8" t="inlineStr">
@@ -45237,7 +45237,7 @@
       </c>
       <c r="F288" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G288" s="8" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P288" s="8" t="inlineStr">
@@ -45318,7 +45318,7 @@
       </c>
       <c r="F289" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G289" s="8" t="inlineStr">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P289" s="8" t="inlineStr">
@@ -45399,7 +45399,7 @@
       </c>
       <c r="F290" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G290" s="8" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P290" s="8" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="F291" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G291" s="8" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P291" s="8" t="inlineStr">
@@ -45557,7 +45557,7 @@
       </c>
       <c r="F292" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G292" s="8" t="inlineStr">
@@ -45593,7 +45593,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P292" s="8" t="inlineStr">
@@ -45634,7 +45634,7 @@
       </c>
       <c r="F293" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G293" s="8" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P293" s="8" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="F294" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G294" s="8" t="inlineStr">
@@ -45747,7 +45747,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P294" s="8" t="inlineStr">
@@ -46501,7 +46501,7 @@
       </c>
       <c r="F304" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G304" s="8" t="inlineStr">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P304" s="8" t="inlineStr">
@@ -46898,7 +46898,7 @@
       </c>
       <c r="F309" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G309" s="8" t="inlineStr">
@@ -46938,7 +46938,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P309" s="8" t="inlineStr">
@@ -46979,7 +46979,7 @@
       </c>
       <c r="F310" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G310" s="8" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P310" s="8" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -2177,7 +2177,7 @@
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>maiReport 식이 참조·설정 데이터 · v1.3.0</t>
+          <t>maiReport 식이 참조·설정 데이터 · v1.4.0</t>
         </is>
       </c>
       <c r="B1" s="24" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
@@ -2195,7 +2195,7 @@
     <row r="2" ht="37.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.3.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
+          <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.4.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -2884,7 +2884,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>바뀐 내용 · 2026-10-14</t>
+          <t>바뀐 내용 · 2026-10-19</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2894,7 +2894,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>v1.1.0 · v1.2.0 · v1.3.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다.</t>
+          <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다.</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -3102,6 +3102,116 @@
       <c r="D58" s="26" t="inlineStr">
         <is>
           <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 특정 음식 (v1.4.0 · 10-19)</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>「라면 국물은 남기기」「치킨 대신 닭백숙」「김치는 백김치로」처럼 특정 음식 이름이 들어가 그 음식을 안 먹는 사람에게는 어색함</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>음식 이름을 음식 종류로 바꿈. 예: 라면 국물은 남기기 → 국물 음식은 국물 남기기, 치킨 대신 닭백숙 → 튀긴 닭 대신 삶은 닭, 김치는 백김치로 → 절임 반찬은 덜 짠 것으로. 함께 세 끼 어제처럼 먹기 → 세 끼 제때 먹기, 저녁 어제처럼 먹기 → 저녁은 제때 먹기, 한 숟갈 양을 절반으로 → 한 숟갈 양, 절반만, 다음 끼니는 챙기기 → 다음 끼니 잘 챙기기. 문구 ID · 축 · 단계 · 성격 · 노출조건은 그대로. 대상 DIET-P-0004 · DIET-P-0033 · DIET-P-0054 · DIET-P-0056 · DIET-P-0078 · DIET-P-0107 · DIET-P-0110 · DIET-P-0114 · DIET-P-0215 · DIET-P-0267 · DIET-P-0287 · DIET-P-0289 · DIET-P-0293 · DIET-P-0306 · DIET-P-0313 · DIET-P-0315 · DIET-P-0334 · DIET-P-0344 · DIET-P-0345 · DIET-P-0359 · DIET-P-0379 · DIET-P-0380 · DIET-P-0383 · DIET-P-0384 · DIET-P-0385 · DIET-P-0386 · DIET-P-0387 · DIET-P-0388 · DIET-P-0389 · DIET-P-0390 · DIET-P-0392 · DIET-P-0394 · DIET-P-0395 · DIET-P-0396 · DIET-P-0397 · DIET-P-0398 · DIET-P-0400 · DIET-P-0401 · DIET-P-0402 · DIET-P-0403 · DIET-P-0404 · DIET-P-0405 · DIET-P-0406</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 타일 문구 · 글자수 · 풀어 쓴 문구 · 이유 한 줄 · 적용 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 혼자 · 가족 · 도시락 (10-19)</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>「혼밥에도」「도시락에」「가족 반찬에」「함께 먹는 끼니」처럼 혼자 사는지 · 가족이 있는지 · 도시락을 싸는지를 전제함</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>누구나 쓸 수 있게 바꿈. 예: 혼밥에도 채소 한 가지 → 간단히 먹어도 채소 하나, 도시락에 달걀 하나 → 달걀 반찬 하나 챙기기, 가족 반찬에 채소 하나 → 상 차릴 때 채소 하나 더, 함께 먹는 끼니 정하기 → 하루 한 끼는 여유 있게. 대상 DIET-P-0204 · DIET-P-0205 · DIET-P-0206 · DIET-P-0207 · DIET-P-0208 · DIET-P-0209 · DIET-P-0210 · DIET-P-0211 · DIET-P-0212 · DIET-P-0213 · DIET-P-0328 · DIET-P-0378</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>입문 문구 넓히기 (10-19)</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「면 국물은 반만」「면 요리에 달걀 하나」「분말 스프는 반만」처럼 음식 종류가 좁은 문구가 있음</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>입문은 누구나 바로 할 수 있게 넓게 씀. 예: 국물 음식은 절반만, 끓일 때 달걀 하나 넣기, 양념은 절반만 넣기. 대상 DIET-P-0215 · DIET-P-0344 · DIET-P-0394 · DIET-P-0397 · DIET-P-0403</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>문구 다듬기 · 효과가 드러나게 (10-19)</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」이 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>입문 「A 대신 B」 → 기본 단계 (10-19)</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「국 대신 나물 반찬」「튀김 대신 구이 · 찜」처럼 무엇을 먹고 있다는 전제가 있는 바꾸기 문구 20개가 있음</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>20개를 입문 → 기본 단계로 옮김(야식 대신 물 한 잔 · 야식 대신 따뜻한 차는 입문 유지). 문구 ID · 문구 버전 · 축은 그대로. 옮긴 뒤에도 축마다 입문 문구 17개 이상. 대상 DIET-P-0044 · 0050 · 0075 · 0126 · 0260 · 0290 · 0298 · 0299 · 0379 · 0380 · 0384~0390 · 0400 · 0405 · 0406</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 단계(입문 → 기본) · 적용 메모</t>
         </is>
       </c>
     </row>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」이 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
+          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」「외식에도 채소 하나 더」가 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴는 채소 위주로. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -25298,20 +25298,20 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>외식에도 채소 하나 더</t>
+          <t>외식 메뉴는 채소 위주로</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>밖에서 먹을 때도 채소가 들어간 메뉴나 반찬을 하나 더 골라 보세요.</t>
+          <t>밖에서 먹을 때는 비빔밥 · 쌈밥처럼 채소가 많이 든 메뉴를 골라 보세요.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>외식할 때 채소 메뉴가 있는지 살펴봐요.</t>
+          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴는 채소 위주로. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -25298,20 +25298,20 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>외식 메뉴는 채소 위주로</t>
+          <t>외식 메뉴, 채소 곁들이기</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>밖에서 먹을 때는 비빔밥 · 쌈밥처럼 채소가 많이 든 메뉴를 골라 보세요.</t>
+          <t>밖에서 먹을 때도 나물 · 쌈 같은 채소 반찬을 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
+          <t>채소를 곁들이면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로 · 10-19 외식 메뉴에 채소 곁들이기로</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기 · 먹기 편한 시간 적어보기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0292 · DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -38164,7 +38164,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>먹기 편한 시간 적기</t>
+          <t>먹기 편한 시간 적어보기</t>
         </is>
       </c>
       <c r="H196" s="8">
@@ -38195,7 +38195,7 @@
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 19번)</t>
+          <t>10-13 추가(검수표 19번) · 10-19 「적어보기」로</t>
         </is>
       </c>
       <c r="P196" s="8" t="inlineStr">

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\docs\엔진\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E3EBE0-D206-4B04-935A-27AA402A1F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89991B6-AFEE-46D5-B31B-CB1798F15371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42240" yWindow="2460" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10419,7 +10419,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10489,6 +10489,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -10532,7 +10545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10606,6 +10619,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13222,16 +13244,16 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="52">
-      <c r="A64" s="26" t="s">
+      <c r="A64" s="31" t="s">
         <v>3450</v>
       </c>
-      <c r="B64" s="26" t="s">
+      <c r="B64" s="31" t="s">
         <v>3451</v>
       </c>
-      <c r="C64" s="26" t="s">
+      <c r="C64" s="31" t="s">
         <v>3452</v>
       </c>
-      <c r="D64" s="26" t="s">
+      <c r="D64" s="31" t="s">
         <v>3453</v>
       </c>
     </row>
@@ -45357,7 +45379,7 @@
         <v>3308</v>
       </c>
       <c r="H370" s="8">
-        <f t="shared" ref="H370:H433" si="3">LEN(G370)</f>
+        <f t="shared" ref="H370:H404" si="3">LEN(G370)</f>
         <v>12</v>
       </c>
       <c r="I370" s="4" t="s">
@@ -48443,7 +48465,7 @@
       <c r="C23" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="30">
         <v>365</v>
       </c>
       <c r="E23" s="4"/>
@@ -48453,7 +48475,7 @@
       <c r="G23" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="30" t="s">
         <v>3449</v>
       </c>
     </row>
@@ -50884,13 +50906,13 @@
       <c r="C64" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="29" t="s">
         <v>3447</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="29" t="s">
         <v>3448</v>
       </c>
     </row>

--- a/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/docs/엔진/식이/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\docs\엔진\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760818AA-A74D-47D5-B7B2-5CBA6836D01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B362AAA8-E992-497D-A203-D4371053658E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11028" uniqueCount="3454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11043" uniqueCount="3458">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · v1.4.0</t>
   </si>
@@ -10412,7 +10412,83 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. · 최근 것이 위</t>
+    <t>상태</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>전달</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>반영</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+  </si>
+  <si>
+    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. · 최근 것이 위 · 반영 완료 8건은 맨 아래에 숨김(행 번호 사이를 우클릭 → 숨기기 취소)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10420,7 +10496,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10503,8 +10579,47 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10532,6 +10647,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -10546,7 +10679,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10630,6 +10763,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12510,11 +12652,11 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -13034,15 +13176,15 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
     </row>
-    <row r="48" spans="1:4" ht="25">
+    <row r="48" spans="1:4" ht="37.5">
       <c r="A48" s="4" t="s">
-        <v>3453</v>
+        <v>3457</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:5">
       <c r="A50" s="4" t="s">
         <v>88</v>
       </c>
@@ -13055,8 +13197,11 @@
       <c r="D50" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="52">
+      <c r="E50" s="4" t="s">
+        <v>3453</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="52">
       <c r="A51" s="31" t="s">
         <v>3449</v>
       </c>
@@ -13069,148 +13214,181 @@
       <c r="D51" s="31" t="s">
         <v>3452</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="52">
+      <c r="E51" s="32" t="s">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="39">
       <c r="A52" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="26">
+      <c r="A53" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="26">
+      <c r="A54" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="26">
+      <c r="A55" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="39" customHeight="1">
+      <c r="A56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>3455</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="52" hidden="1">
+      <c r="A57" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B57" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C57" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="D52" s="26" t="s">
+      <c r="D57" s="26" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="65">
-      <c r="A53" s="26" t="s">
+      <c r="E57" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="65" hidden="1">
+      <c r="A58" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="B58" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C58" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="D53" s="26" t="s">
+      <c r="D58" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="39">
-      <c r="A54" s="26" t="s">
+      <c r="E58" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="39" hidden="1">
+      <c r="A59" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B59" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C59" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="D54" s="26" t="s">
+      <c r="D59" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="78">
-      <c r="A55" s="26" t="s">
+      <c r="E59" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="78" hidden="1">
+      <c r="A60" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B60" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C60" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="D55" s="26" t="s">
+      <c r="D60" s="26" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="182">
-      <c r="A56" s="26" t="s">
+      <c r="E60" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="182" hidden="1">
+      <c r="A61" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="B61" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C56" s="26" t="s">
+      <c r="C61" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="D56" s="26" t="s">
+      <c r="D61" s="26" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="39">
-      <c r="A57" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D57" s="26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="26">
-      <c r="A58" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B58" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="26">
-      <c r="A59" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="26">
-      <c r="A60" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="39" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B61" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="39" customHeight="1">
+      <c r="E61" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A62" s="26" t="s">
         <v>100</v>
       </c>
@@ -13223,8 +13401,11 @@
       <c r="D62" s="26" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="39" customHeight="1">
+      <c r="E62" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A63" s="26" t="s">
         <v>96</v>
       </c>
@@ -13237,8 +13418,11 @@
       <c r="D63" s="26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63" s="34" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" hidden="1">
       <c r="A64" s="26" t="s">
         <v>92</v>
       </c>
@@ -13250,6 +13434,9 @@
       </c>
       <c r="D64" s="26" t="s">
         <v>95</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>3456</v>
       </c>
     </row>
   </sheetData>
